--- a/nobunaga/50Fief.xlsx
+++ b/nobunaga/50Fief.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Chris.Isaacson\Vault\projects\game-annotation\nobunaga\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{52BF504E-224A-4120-B0CB-2D8729CA4FDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A5D043F-3137-4434-AF69-1BD0EAD9385B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-255" windowWidth="29040" windowHeight="17520" xr2:uid="{1993C710-027D-4F86-A27A-587E55370941}"/>
   </bookViews>
@@ -16,14 +16,27 @@
     <sheet name="50Fief" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'50Fief'!$A$1:$AD$51</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'50Fief'!$A$1:$AL$51</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="172">
   <si>
     <t>idx</t>
   </si>
@@ -518,6 +531,27 @@
   </si>
   <si>
     <t>16th</t>
+  </si>
+  <si>
+    <t>55taxL</t>
+  </si>
+  <si>
+    <t>%R</t>
+  </si>
+  <si>
+    <t>FreeR</t>
+  </si>
+  <si>
+    <t>Give</t>
+  </si>
+  <si>
+    <t>FinalL</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>f17R</t>
   </si>
 </sst>
 </file>
@@ -1014,11 +1048,13 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="10" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1394,7 +1430,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0EA501B-F4E9-40F5-BCE6-EA7716C70CE7}">
-  <dimension ref="A1:AG51"/>
+  <dimension ref="A1:AL51"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.5703125" bestFit="1" customWidth="1"/>
@@ -1428,9 +1464,10 @@
     <col min="30" max="30" width="6.7109375" customWidth="1"/>
     <col min="31" max="31" width="4.28515625" bestFit="1" customWidth="1"/>
     <col min="32" max="32" width="14" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="10.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1524,8 +1561,29 @@
       <c r="AE1" t="s">
         <v>127</v>
       </c>
+      <c r="AF1" t="s">
+        <v>170</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>171</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>165</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>166</v>
+      </c>
+      <c r="AJ1" t="s">
+        <v>167</v>
+      </c>
+      <c r="AK1" t="s">
+        <v>168</v>
+      </c>
+      <c r="AL1" t="s">
+        <v>169</v>
+      </c>
     </row>
-    <row r="2" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>24</v>
       </c>
@@ -1629,8 +1687,28 @@
       <c r="AG2" t="s">
         <v>147</v>
       </c>
+      <c r="AH2">
+        <f>0.65*J2</f>
+        <v>46.15</v>
+      </c>
+      <c r="AI2" s="4">
+        <f>1-(AH2^2/2025)</f>
+        <v>-5.1764197530864031E-2</v>
+      </c>
+      <c r="AJ2">
+        <f>G2-(2/3*L2)</f>
+        <v>28</v>
+      </c>
+      <c r="AK2">
+        <f>2*((5*AJ2)/(SQRT(((H2+AH2)/2)+AJ2)))</f>
+        <v>29.339887305484748</v>
+      </c>
+      <c r="AL2">
+        <f>AH2+AK2</f>
+        <v>75.489887305484743</v>
+      </c>
     </row>
-    <row r="3" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>23</v>
       </c>
@@ -1734,8 +1812,28 @@
       <c r="AG3" t="s">
         <v>147</v>
       </c>
+      <c r="AH3">
+        <f>0.65*J3</f>
+        <v>49.4</v>
+      </c>
+      <c r="AI3" s="4">
+        <f>1-(AH3^2/2025)</f>
+        <v>-0.20511604938271599</v>
+      </c>
+      <c r="AJ3">
+        <f>G3-(2/3*L3)</f>
+        <v>27.666666666666671</v>
+      </c>
+      <c r="AK3">
+        <f>2*((5*AJ3)/(SQRT(((H3+AH3)/2)+AJ3)))</f>
+        <v>28.787185221212997</v>
+      </c>
+      <c r="AL3">
+        <f>AH3+AK3</f>
+        <v>78.187185221212999</v>
+      </c>
     </row>
-    <row r="4" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>45</v>
       </c>
@@ -1836,8 +1934,28 @@
       <c r="AF4" t="s">
         <v>138</v>
       </c>
+      <c r="AH4">
+        <f>0.65*J4</f>
+        <v>45.5</v>
+      </c>
+      <c r="AI4" s="4">
+        <f>1-(AH4^2/2025)</f>
+        <v>-2.2345679012345743E-2</v>
+      </c>
+      <c r="AJ4">
+        <f>G4-(2/3*L4)</f>
+        <v>22.333333333333336</v>
+      </c>
+      <c r="AK4">
+        <f>2*((5*AJ4)/(SQRT(((H4+AH4)/2)+AJ4)))</f>
+        <v>24.3555862605375</v>
+      </c>
+      <c r="AL4">
+        <f>AH4+AK4</f>
+        <v>69.855586260537507</v>
+      </c>
     </row>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>38</v>
       </c>
@@ -1938,8 +2056,28 @@
       <c r="AF5" t="s">
         <v>137</v>
       </c>
+      <c r="AH5">
+        <f>0.65*J5</f>
+        <v>51.35</v>
+      </c>
+      <c r="AI5" s="4">
+        <f>1-(AH5^2/2025)</f>
+        <v>-0.30213456790123461</v>
+      </c>
+      <c r="AJ5">
+        <f>G5-(2/3*L5)</f>
+        <v>2.6666666666666714</v>
+      </c>
+      <c r="AK5">
+        <f>2*((5*AJ5)/(SQRT(((H5+AH5)/2)+AJ5)))</f>
+        <v>3.8156936087657392</v>
+      </c>
+      <c r="AL5">
+        <f>AH5+AK5</f>
+        <v>55.165693608765743</v>
+      </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>13</v>
       </c>
@@ -2043,8 +2181,28 @@
       <c r="AG6" t="s">
         <v>148</v>
       </c>
+      <c r="AH6">
+        <f>0.65*J6</f>
+        <v>40.950000000000003</v>
+      </c>
+      <c r="AI6" s="4">
+        <f>1-(AH6^2/2025)</f>
+        <v>0.17189999999999994</v>
+      </c>
+      <c r="AJ6">
+        <f>G6-(2/3*L6)</f>
+        <v>33.333333333333336</v>
+      </c>
+      <c r="AK6">
+        <f>2*((5*AJ6)/(SQRT(((H6+AH6)/2)+AJ6)))</f>
+        <v>34.415813156121459</v>
+      </c>
+      <c r="AL6">
+        <f>AH6+AK6</f>
+        <v>75.365813156121462</v>
+      </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>42</v>
       </c>
@@ -2145,8 +2303,28 @@
       <c r="AF7" t="s">
         <v>140</v>
       </c>
+      <c r="AH7">
+        <f>0.65*J7</f>
+        <v>45.5</v>
+      </c>
+      <c r="AI7" s="4">
+        <f>1-(AH7^2/2025)</f>
+        <v>-2.2345679012345743E-2</v>
+      </c>
+      <c r="AJ7">
+        <f>G7-(2/3*L7)</f>
+        <v>21</v>
+      </c>
+      <c r="AK7">
+        <f>2*((5*AJ7)/(SQRT(((H7+AH7)/2)+AJ7)))</f>
+        <v>23.739803595657303</v>
+      </c>
+      <c r="AL7">
+        <f>AH7+AK7</f>
+        <v>69.239803595657307</v>
+      </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>9</v>
       </c>
@@ -2250,8 +2428,28 @@
       <c r="AG8" t="s">
         <v>149</v>
       </c>
+      <c r="AH8">
+        <f>0.65*J8</f>
+        <v>51.35</v>
+      </c>
+      <c r="AI8" s="4">
+        <f>1-(AH8^2/2025)</f>
+        <v>-0.30213456790123461</v>
+      </c>
+      <c r="AJ8">
+        <f>G8-(2/3*L8)</f>
+        <v>29.666666666666671</v>
+      </c>
+      <c r="AK8">
+        <f>2*((5*AJ8)/(SQRT(((H8+AH8)/2)+AJ8)))</f>
+        <v>30.382771129651221</v>
+      </c>
+      <c r="AL8">
+        <f>AH8+AK8</f>
+        <v>81.732771129651226</v>
+      </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>14</v>
       </c>
@@ -2355,8 +2553,28 @@
       <c r="AG9" t="s">
         <v>152</v>
       </c>
+      <c r="AH9">
+        <f>0.65*J9</f>
+        <v>48.1</v>
+      </c>
+      <c r="AI9" s="4">
+        <f>1-(AH9^2/2025)</f>
+        <v>-0.14252345679012346</v>
+      </c>
+      <c r="AJ9" s="3">
+        <f>G9-(2/3*L9)</f>
+        <v>-8</v>
+      </c>
+      <c r="AK9">
+        <f>2*((5*AJ9)/(SQRT(((H9+AH9)/2)+AJ9)))</f>
+        <v>-12.80204849165111</v>
+      </c>
+      <c r="AL9" s="3">
+        <f>AH9+AK9</f>
+        <v>35.297951508348888</v>
+      </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>32</v>
       </c>
@@ -2460,8 +2678,28 @@
       <c r="AG10" t="s">
         <v>151</v>
       </c>
+      <c r="AH10">
+        <f>0.65*J10</f>
+        <v>42.25</v>
+      </c>
+      <c r="AI10" s="4">
+        <f>1-(AH10^2/2025)</f>
+        <v>0.11848765432098762</v>
+      </c>
+      <c r="AJ10">
+        <f>G10-(2/3*L10)</f>
+        <v>23</v>
+      </c>
+      <c r="AK10">
+        <f>2*((5*AJ10)/(SQRT(((H10+AH10)/2)+AJ10)))</f>
+        <v>26.448140430499173</v>
+      </c>
+      <c r="AL10">
+        <f>AH10+AK10</f>
+        <v>68.698140430499166</v>
+      </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>25</v>
       </c>
@@ -2565,8 +2803,28 @@
       <c r="AG11" t="s">
         <v>150</v>
       </c>
+      <c r="AH11">
+        <f>0.65*J11</f>
+        <v>42.25</v>
+      </c>
+      <c r="AI11" s="4">
+        <f>1-(AH11^2/2025)</f>
+        <v>0.11848765432098762</v>
+      </c>
+      <c r="AJ11">
+        <f>G11-(2/3*L11)</f>
+        <v>2.6666666666666714</v>
+      </c>
+      <c r="AK11">
+        <f>2*((5*AJ11)/(SQRT(((H11+AH11)/2)+AJ11)))</f>
+        <v>3.8573819521220436</v>
+      </c>
+      <c r="AL11">
+        <f>AH11+AK11</f>
+        <v>46.10738195212204</v>
+      </c>
     </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>26</v>
       </c>
@@ -2670,8 +2928,28 @@
       <c r="AG12" t="s">
         <v>153</v>
       </c>
+      <c r="AH12">
+        <f>0.65*J12</f>
+        <v>37.700000000000003</v>
+      </c>
+      <c r="AI12" s="4">
+        <f>1-(AH12^2/2025)</f>
+        <v>0.29812839506172828</v>
+      </c>
+      <c r="AJ12">
+        <f>G12-(2/3*L12)</f>
+        <v>30.333333333333336</v>
+      </c>
+      <c r="AK12">
+        <f>2*((5*AJ12)/(SQRT(((H12+AH12)/2)+AJ12)))</f>
+        <v>34.415668618263226</v>
+      </c>
+      <c r="AL12">
+        <f>AH12+AK12</f>
+        <v>72.115668618263228</v>
+      </c>
     </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>21</v>
       </c>
@@ -2775,8 +3053,28 @@
       <c r="AG13" t="s">
         <v>154</v>
       </c>
+      <c r="AH13">
+        <f>0.65*J13</f>
+        <v>38.35</v>
+      </c>
+      <c r="AI13" s="4">
+        <f>1-(AH13^2/2025)</f>
+        <v>0.27371728395061723</v>
+      </c>
+      <c r="AJ13">
+        <f>G13-(2/3*L13)</f>
+        <v>26.666666666666671</v>
+      </c>
+      <c r="AK13">
+        <f>2*((5*AJ13)/(SQRT(((H13+AH13)/2)+AJ13)))</f>
+        <v>29.658631154382181</v>
+      </c>
+      <c r="AL13">
+        <f>AH13+AK13</f>
+        <v>68.008631154382186</v>
+      </c>
     </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>19</v>
       </c>
@@ -2880,8 +3178,28 @@
       <c r="AG14" t="s">
         <v>155</v>
       </c>
+      <c r="AH14">
+        <f>0.65*J14</f>
+        <v>42.25</v>
+      </c>
+      <c r="AI14" s="4">
+        <f>1-(AH14^2/2025)</f>
+        <v>0.11848765432098762</v>
+      </c>
+      <c r="AJ14" s="3">
+        <f>G14-(2/3*L14)</f>
+        <v>-0.6666666666666643</v>
+      </c>
+      <c r="AK14">
+        <f>2*((5*AJ14)/(SQRT(((H14+AH14)/2)+AJ14)))</f>
+        <v>-1.0171500602514383</v>
+      </c>
+      <c r="AL14" s="3">
+        <f>AH14+AK14</f>
+        <v>41.232849939748561</v>
+      </c>
     </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>49</v>
       </c>
@@ -2982,8 +3300,28 @@
       <c r="AF15" t="s">
         <v>145</v>
       </c>
+      <c r="AH15">
+        <f>0.65*J15</f>
+        <v>42.25</v>
+      </c>
+      <c r="AI15" s="4">
+        <f>1-(AH15^2/2025)</f>
+        <v>0.11848765432098762</v>
+      </c>
+      <c r="AJ15">
+        <f>G15-(2/3*L15)</f>
+        <v>7</v>
+      </c>
+      <c r="AK15">
+        <f>2*((5*AJ15)/(SQRT(((H15+AH15)/2)+AJ15)))</f>
+        <v>9.742446008949095</v>
+      </c>
+      <c r="AL15">
+        <f>AH15+AK15</f>
+        <v>51.992446008949095</v>
+      </c>
     </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>30</v>
       </c>
@@ -3087,8 +3425,28 @@
       <c r="AG16" t="s">
         <v>156</v>
       </c>
+      <c r="AH16">
+        <f>0.65*J16</f>
+        <v>24.7</v>
+      </c>
+      <c r="AI16" s="5">
+        <f>1-(AH16^2/2025)</f>
+        <v>0.698720987654321</v>
+      </c>
+      <c r="AJ16">
+        <f>G16-(2/3*L16)</f>
+        <v>22.333333333333336</v>
+      </c>
+      <c r="AK16">
+        <f>2*((5*AJ16)/(SQRT(((H16+AH16)/2)+AJ16)))</f>
+        <v>27.662107529254303</v>
+      </c>
+      <c r="AL16">
+        <f>AH16+AK16</f>
+        <v>52.362107529254303</v>
+      </c>
     </row>
-    <row r="17" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>17</v>
       </c>
@@ -3192,8 +3550,28 @@
       <c r="AG17" t="s">
         <v>157</v>
       </c>
+      <c r="AH17">
+        <f>0.65*J17</f>
+        <v>47.45</v>
+      </c>
+      <c r="AI17" s="4">
+        <f>1-(AH17^2/2025)</f>
+        <v>-0.11185308641975311</v>
+      </c>
+      <c r="AJ17">
+        <f>G17-(2/3*L17)</f>
+        <v>0</v>
+      </c>
+      <c r="AK17">
+        <f>2*((5*AJ17)/(SQRT(((H17+AH17)/2)+AJ17)))</f>
+        <v>0</v>
+      </c>
+      <c r="AL17">
+        <f>AH17+AK17</f>
+        <v>47.45</v>
+      </c>
     </row>
-    <row r="18" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>5</v>
       </c>
@@ -3294,8 +3672,28 @@
       <c r="AF18" t="s">
         <v>145</v>
       </c>
+      <c r="AH18">
+        <f>0.65*J18</f>
+        <v>37.700000000000003</v>
+      </c>
+      <c r="AI18" s="4">
+        <f>1-(AH18^2/2025)</f>
+        <v>0.29812839506172828</v>
+      </c>
+      <c r="AJ18">
+        <f>G18-(2/3*L18)</f>
+        <v>6.3333333333333357</v>
+      </c>
+      <c r="AK18">
+        <f>2*((5*AJ18)/(SQRT(((H18+AH18)/2)+AJ18)))</f>
+        <v>9.5824036452765782</v>
+      </c>
+      <c r="AL18">
+        <f>AH18+AK18</f>
+        <v>47.282403645276581</v>
+      </c>
     </row>
-    <row r="19" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>36</v>
       </c>
@@ -3396,8 +3794,28 @@
       <c r="AF19" t="s">
         <v>145</v>
       </c>
+      <c r="AH19">
+        <f>0.65*J19</f>
+        <v>33.800000000000004</v>
+      </c>
+      <c r="AI19" s="4">
+        <f>1-(AH19^2/2025)</f>
+        <v>0.43583209876543194</v>
+      </c>
+      <c r="AJ19">
+        <f>G19-(2/3*L19)</f>
+        <v>9.3333333333333357</v>
+      </c>
+      <c r="AK19">
+        <f>2*((5*AJ19)/(SQRT(((H19+AH19)/2)+AJ19)))</f>
+        <v>13.801311186847087</v>
+      </c>
+      <c r="AL19">
+        <f>AH19+AK19</f>
+        <v>47.601311186847092</v>
+      </c>
     </row>
-    <row r="20" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>39</v>
       </c>
@@ -3498,8 +3916,28 @@
       <c r="AF20" t="s">
         <v>5</v>
       </c>
+      <c r="AH20">
+        <f>0.65*J20</f>
+        <v>27.3</v>
+      </c>
+      <c r="AI20" s="5">
+        <f>1-(AH20^2/2025)</f>
+        <v>0.63195555555555549</v>
+      </c>
+      <c r="AJ20">
+        <f>G20-(2/3*L20)</f>
+        <v>27</v>
+      </c>
+      <c r="AK20">
+        <f>2*((5*AJ20)/(SQRT(((H20+AH20)/2)+AJ20)))</f>
+        <v>32.236651665768576</v>
+      </c>
+      <c r="AL20">
+        <f>AH20+AK20</f>
+        <v>59.536651665768574</v>
+      </c>
     </row>
-    <row r="21" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>10</v>
       </c>
@@ -3600,8 +4038,28 @@
       <c r="AF21" t="s">
         <v>5</v>
       </c>
+      <c r="AH21">
+        <f>0.65*J21</f>
+        <v>33.15</v>
+      </c>
+      <c r="AI21" s="4">
+        <f>1-(AH21^2/2025)</f>
+        <v>0.4573222222222223</v>
+      </c>
+      <c r="AJ21">
+        <f>G21-(2/3*L21)</f>
+        <v>7.3333333333333357</v>
+      </c>
+      <c r="AK21">
+        <f>2*((5*AJ21)/(SQRT(((H21+AH21)/2)+AJ21)))</f>
+        <v>10.277961500537783</v>
+      </c>
+      <c r="AL21" s="3">
+        <f>AH21+AK21</f>
+        <v>43.427961500537783</v>
+      </c>
     </row>
-    <row r="22" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>20</v>
       </c>
@@ -3705,8 +4163,28 @@
       <c r="AG22" t="s">
         <v>159</v>
       </c>
+      <c r="AH22">
+        <f>0.65*J22</f>
+        <v>48.1</v>
+      </c>
+      <c r="AI22" s="4">
+        <f>1-(AH22^2/2025)</f>
+        <v>-0.14252345679012346</v>
+      </c>
+      <c r="AJ22">
+        <f>G22-(2/3*L22)</f>
+        <v>30.666666666666668</v>
+      </c>
+      <c r="AK22">
+        <f>2*((5*AJ22)/(SQRT(((H22+AH22)/2)+AJ22)))</f>
+        <v>33.220357474399719</v>
+      </c>
+      <c r="AL22">
+        <f>AH22+AK22</f>
+        <v>81.320357474399714</v>
+      </c>
     </row>
-    <row r="23" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>46</v>
       </c>
@@ -3807,8 +4285,28 @@
       <c r="AF23" t="s">
         <v>161</v>
       </c>
+      <c r="AH23">
+        <f>0.65*J23</f>
+        <v>23.400000000000002</v>
+      </c>
+      <c r="AI23" s="5">
+        <f>1-(AH23^2/2025)</f>
+        <v>0.72960000000000003</v>
+      </c>
+      <c r="AJ23">
+        <f>G23-(2/3*L23)</f>
+        <v>23.666666666666671</v>
+      </c>
+      <c r="AK23">
+        <f>2*((5*AJ23)/(SQRT(((H23+AH23)/2)+AJ23)))</f>
+        <v>29.161123437000203</v>
+      </c>
+      <c r="AL23">
+        <f>AH23+AK23</f>
+        <v>52.561123437000205</v>
+      </c>
     </row>
-    <row r="24" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>6</v>
       </c>
@@ -3909,8 +4407,28 @@
       <c r="AF24" t="s">
         <v>143</v>
       </c>
+      <c r="AH24">
+        <f>0.65*J24</f>
+        <v>21.45</v>
+      </c>
+      <c r="AI24" s="5">
+        <f>1-(AH24^2/2025)</f>
+        <v>0.77278888888888897</v>
+      </c>
+      <c r="AJ24">
+        <f>G24-(2/3*L24)</f>
+        <v>20.666666666666668</v>
+      </c>
+      <c r="AK24">
+        <f>2*((5*AJ24)/(SQRT(((H24+AH24)/2)+AJ24)))</f>
+        <v>27.399718840696014</v>
+      </c>
+      <c r="AL24">
+        <f>AH24+AK24</f>
+        <v>48.849718840696013</v>
+      </c>
     </row>
-    <row r="25" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>4</v>
       </c>
@@ -4011,8 +4529,28 @@
       <c r="AF25" t="s">
         <v>162</v>
       </c>
+      <c r="AH25">
+        <f>0.65*J25</f>
+        <v>34.450000000000003</v>
+      </c>
+      <c r="AI25" s="4">
+        <f>1-(AH25^2/2025)</f>
+        <v>0.41392469135802457</v>
+      </c>
+      <c r="AJ25">
+        <f>G25-(2/3*L25)</f>
+        <v>24.333333333333336</v>
+      </c>
+      <c r="AK25">
+        <f>2*((5*AJ25)/(SQRT(((H25+AH25)/2)+AJ25)))</f>
+        <v>28.968596097495787</v>
+      </c>
+      <c r="AL25">
+        <f>AH25+AK25</f>
+        <v>63.418596097495794</v>
+      </c>
     </row>
-    <row r="26" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>12</v>
       </c>
@@ -4113,8 +4651,28 @@
       <c r="AF26" t="s">
         <v>143</v>
       </c>
+      <c r="AH26">
+        <f>0.65*J26</f>
+        <v>37.700000000000003</v>
+      </c>
+      <c r="AI26" s="4">
+        <f>1-(AH26^2/2025)</f>
+        <v>0.29812839506172828</v>
+      </c>
+      <c r="AJ26" s="3">
+        <f>G26-(2/3*L26)</f>
+        <v>-8.6666666666666643</v>
+      </c>
+      <c r="AK26">
+        <f>2*((5*AJ26)/(SQRT(((H26+AH26)/2)+AJ26)))</f>
+        <v>-16.62266826798378</v>
+      </c>
+      <c r="AL26" s="3">
+        <f>AH26+AK26</f>
+        <v>21.077331732016223</v>
+      </c>
     </row>
-    <row r="27" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>8</v>
       </c>
@@ -4212,8 +4770,28 @@
       <c r="AE27" t="s">
         <v>132</v>
       </c>
+      <c r="AH27">
+        <f>0.65*J27</f>
+        <v>46.800000000000004</v>
+      </c>
+      <c r="AI27" s="4">
+        <f>1-(AH27^2/2025)</f>
+        <v>-8.1600000000000117E-2</v>
+      </c>
+      <c r="AJ27">
+        <f>G27-(2/3*L27)</f>
+        <v>15.666666666666668</v>
+      </c>
+      <c r="AK27">
+        <f>2*((5*AJ27)/(SQRT(((H27+AH27)/2)+AJ27)))</f>
+        <v>21.208643443403631</v>
+      </c>
+      <c r="AL27">
+        <f>AH27+AK27</f>
+        <v>68.008643443403628</v>
+      </c>
     </row>
-    <row r="28" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>33</v>
       </c>
@@ -4311,8 +4889,28 @@
       <c r="AE28" t="s">
         <v>132</v>
       </c>
+      <c r="AH28">
+        <f>0.65*J28</f>
+        <v>27.95</v>
+      </c>
+      <c r="AI28" s="5">
+        <f>1-(AH28^2/2025)</f>
+        <v>0.61422098765432098</v>
+      </c>
+      <c r="AJ28">
+        <f>G28-(2/3*L28)</f>
+        <v>32</v>
+      </c>
+      <c r="AK28">
+        <f>2*((5*AJ28)/(SQRT(((H28+AH28)/2)+AJ28)))</f>
+        <v>36.956577171035917</v>
+      </c>
+      <c r="AL28">
+        <f>AH28+AK28</f>
+        <v>64.90657717103592</v>
+      </c>
     </row>
-    <row r="29" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>44</v>
       </c>
@@ -4410,8 +5008,28 @@
       <c r="AE29" t="s">
         <v>132</v>
       </c>
+      <c r="AH29">
+        <f>0.65*J29</f>
+        <v>20.8</v>
+      </c>
+      <c r="AI29" s="5">
+        <f>1-(AH29^2/2025)</f>
+        <v>0.78635061728395061</v>
+      </c>
+      <c r="AJ29">
+        <f>G29-(2/3*L29)</f>
+        <v>17.333333333333336</v>
+      </c>
+      <c r="AK29">
+        <f>2*((5*AJ29)/(SQRT(((H29+AH29)/2)+AJ29)))</f>
+        <v>24.456037413713979</v>
+      </c>
+      <c r="AL29">
+        <f>AH29+AK29</f>
+        <v>45.256037413713983</v>
+      </c>
     </row>
-    <row r="30" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>40</v>
       </c>
@@ -4509,8 +5127,28 @@
       <c r="AE30" t="s">
         <v>132</v>
       </c>
+      <c r="AH30">
+        <f>0.65*J30</f>
+        <v>23.400000000000002</v>
+      </c>
+      <c r="AI30" s="5">
+        <f>1-(AH30^2/2025)</f>
+        <v>0.72960000000000003</v>
+      </c>
+      <c r="AJ30">
+        <f>G30-(2/3*L30)</f>
+        <v>32.666666666666671</v>
+      </c>
+      <c r="AK30">
+        <f>2*((5*AJ30)/(SQRT(((H30+AH30)/2)+AJ30)))</f>
+        <v>37.259394836923505</v>
+      </c>
+      <c r="AL30">
+        <f>AH30+AK30</f>
+        <v>60.659394836923511</v>
+      </c>
     </row>
-    <row r="31" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>15</v>
       </c>
@@ -4611,8 +5249,28 @@
       <c r="AG31" t="s">
         <v>160</v>
       </c>
+      <c r="AH31">
+        <f>0.65*J31</f>
+        <v>15.600000000000001</v>
+      </c>
+      <c r="AI31" s="5">
+        <f>1-(AH31^2/2025)</f>
+        <v>0.87982222222222217</v>
+      </c>
+      <c r="AJ31">
+        <f>G31-(2/3*L31)</f>
+        <v>12</v>
+      </c>
+      <c r="AK31">
+        <f>2*((5*AJ31)/(SQRT(((H31+AH31)/2)+AJ31)))</f>
+        <v>20.341905108624314</v>
+      </c>
+      <c r="AL31" s="3">
+        <f>AH31+AK31</f>
+        <v>35.941905108624312</v>
+      </c>
     </row>
-    <row r="32" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>31</v>
       </c>
@@ -4713,8 +5371,28 @@
       <c r="AG32" t="s">
         <v>163</v>
       </c>
+      <c r="AH32">
+        <f>0.65*J32</f>
+        <v>32.5</v>
+      </c>
+      <c r="AI32" s="4">
+        <f>1-(AH32^2/2025)</f>
+        <v>0.47839506172839508</v>
+      </c>
+      <c r="AJ32">
+        <f>G32-(2/3*L32)</f>
+        <v>12.666666666666668</v>
+      </c>
+      <c r="AK32">
+        <f>2*((5*AJ32)/(SQRT(((H32+AH32)/2)+AJ32)))</f>
+        <v>18.492633708592344</v>
+      </c>
+      <c r="AL32">
+        <f>AH32+AK32</f>
+        <v>50.992633708592344</v>
+      </c>
     </row>
-    <row r="33" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>18</v>
       </c>
@@ -4812,8 +5490,28 @@
       <c r="AE33" t="s">
         <v>132</v>
       </c>
+      <c r="AH33">
+        <f>0.65*J33</f>
+        <v>25.35</v>
+      </c>
+      <c r="AI33" s="5">
+        <f>1-(AH33^2/2025)</f>
+        <v>0.68265555555555557</v>
+      </c>
+      <c r="AJ33">
+        <f>G33-(2/3*L33)</f>
+        <v>14</v>
+      </c>
+      <c r="AK33">
+        <f>2*((5*AJ33)/(SQRT(((H33+AH33)/2)+AJ33)))</f>
+        <v>21.430942486056374</v>
+      </c>
+      <c r="AL33">
+        <f>AH33+AK33</f>
+        <v>46.780942486056375</v>
+      </c>
     </row>
-    <row r="34" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>3</v>
       </c>
@@ -4911,8 +5609,28 @@
       <c r="AE34" t="s">
         <v>132</v>
       </c>
+      <c r="AH34">
+        <f>0.65*J34</f>
+        <v>24.7</v>
+      </c>
+      <c r="AI34" s="5">
+        <f>1-(AH34^2/2025)</f>
+        <v>0.698720987654321</v>
+      </c>
+      <c r="AJ34">
+        <f>G34-(2/3*L34)</f>
+        <v>21</v>
+      </c>
+      <c r="AK34">
+        <f>2*((5*AJ34)/(SQRT(((H34+AH34)/2)+AJ34)))</f>
+        <v>28.61715401954347</v>
+      </c>
+      <c r="AL34">
+        <f>AH34+AK34</f>
+        <v>53.317154019543466</v>
+      </c>
     </row>
-    <row r="35" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>47</v>
       </c>
@@ -5010,8 +5728,28 @@
       <c r="AE35" t="s">
         <v>132</v>
       </c>
+      <c r="AH35">
+        <f>0.65*J35</f>
+        <v>29.25</v>
+      </c>
+      <c r="AI35" s="5">
+        <f>1-(AH35^2/2025)</f>
+        <v>0.57750000000000001</v>
+      </c>
+      <c r="AJ35">
+        <f>G35-(2/3*L35)</f>
+        <v>49.333333333333336</v>
+      </c>
+      <c r="AK35">
+        <f>2*((5*AJ35)/(SQRT(((H35+AH35)/2)+AJ35)))</f>
+        <v>50.493274643541781</v>
+      </c>
+      <c r="AL35">
+        <f>AH35+AK35</f>
+        <v>79.743274643541781</v>
+      </c>
     </row>
-    <row r="36" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>28</v>
       </c>
@@ -5109,8 +5847,28 @@
       <c r="AE36" t="s">
         <v>131</v>
       </c>
+      <c r="AH36">
+        <f>0.65*J36</f>
+        <v>20.8</v>
+      </c>
+      <c r="AI36" s="5">
+        <f>1-(AH36^2/2025)</f>
+        <v>0.78635061728395061</v>
+      </c>
+      <c r="AJ36" s="3">
+        <f>G36-(2/3*L36)</f>
+        <v>-5</v>
+      </c>
+      <c r="AK36">
+        <f>2*((5*AJ36)/(SQRT(((H36+AH36)/2)+AJ36)))</f>
+        <v>-12.346619958119872</v>
+      </c>
+      <c r="AL36" s="3">
+        <f>AH36+AK36</f>
+        <v>8.4533800418801288</v>
+      </c>
     </row>
-    <row r="37" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>41</v>
       </c>
@@ -5208,8 +5966,28 @@
       <c r="AE37" t="s">
         <v>131</v>
       </c>
+      <c r="AH37">
+        <f>0.65*J37</f>
+        <v>22.75</v>
+      </c>
+      <c r="AI37" s="5">
+        <f>1-(AH37^2/2025)</f>
+        <v>0.74441358024691362</v>
+      </c>
+      <c r="AJ37">
+        <f>G37-(2/3*L37)</f>
+        <v>42.333333333333336</v>
+      </c>
+      <c r="AK37">
+        <f>2*((5*AJ37)/(SQRT(((H37+AH37)/2)+AJ37)))</f>
+        <v>45.860779364775084</v>
+      </c>
+      <c r="AL37">
+        <f>AH37+AK37</f>
+        <v>68.610779364775084</v>
+      </c>
     </row>
-    <row r="38" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>16</v>
       </c>
@@ -5307,8 +6085,28 @@
       <c r="AE38" t="s">
         <v>131</v>
       </c>
+      <c r="AH38">
+        <f>0.65*J38</f>
+        <v>31.200000000000003</v>
+      </c>
+      <c r="AI38" s="5">
+        <f>1-(AH38^2/2025)</f>
+        <v>0.5192888888888888</v>
+      </c>
+      <c r="AJ38">
+        <f>G38-(2/3*L38)</f>
+        <v>13</v>
+      </c>
+      <c r="AK38">
+        <f>2*((5*AJ38)/(SQRT(((H38+AH38)/2)+AJ38)))</f>
+        <v>20.155644370746373</v>
+      </c>
+      <c r="AL38">
+        <f>AH38+AK38</f>
+        <v>51.355644370746376</v>
+      </c>
     </row>
-    <row r="39" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>22</v>
       </c>
@@ -5409,8 +6207,28 @@
       <c r="AG39" t="s">
         <v>164</v>
       </c>
+      <c r="AH39">
+        <f>0.65*J39</f>
+        <v>20.150000000000002</v>
+      </c>
+      <c r="AI39" s="5">
+        <f>1-(AH39^2/2025)</f>
+        <v>0.79949506172839502</v>
+      </c>
+      <c r="AJ39" s="3">
+        <f>G39-(2/3*L39)</f>
+        <v>-0.33333333333333215</v>
+      </c>
+      <c r="AK39">
+        <f>2*((5*AJ39)/(SQRT(((H39+AH39)/2)+AJ39)))</f>
+        <v>-0.68410559711236441</v>
+      </c>
+      <c r="AL39" s="3">
+        <f>AH39+AK39</f>
+        <v>19.465894402887638</v>
+      </c>
     </row>
-    <row r="40" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>34</v>
       </c>
@@ -5508,8 +6326,28 @@
       <c r="AE40" t="s">
         <v>131</v>
       </c>
+      <c r="AH40">
+        <f>0.65*J40</f>
+        <v>17.55</v>
+      </c>
+      <c r="AI40" s="5">
+        <f>1-(AH40^2/2025)</f>
+        <v>0.84789999999999999</v>
+      </c>
+      <c r="AJ40" s="3">
+        <f>G40-(2/3*L40)</f>
+        <v>-7.3333333333333286</v>
+      </c>
+      <c r="AK40">
+        <f>2*((5*AJ40)/(SQRT(((H40+AH40)/2)+AJ40)))</f>
+        <v>-20.384793729911316</v>
+      </c>
+      <c r="AL40" s="3">
+        <f>AH40+AK40</f>
+        <v>-2.8347937299113148</v>
+      </c>
     </row>
-    <row r="41" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>43</v>
       </c>
@@ -5607,8 +6445,28 @@
       <c r="AE41" t="s">
         <v>131</v>
       </c>
+      <c r="AH41">
+        <f>0.65*J41</f>
+        <v>31.85</v>
+      </c>
+      <c r="AI41" s="4">
+        <f>1-(AH41^2/2025)</f>
+        <v>0.4990506172839505</v>
+      </c>
+      <c r="AJ41">
+        <f>G41-(2/3*L41)</f>
+        <v>21.333333333333336</v>
+      </c>
+      <c r="AK41">
+        <f>2*((5*AJ41)/(SQRT(((H41+AH41)/2)+AJ41)))</f>
+        <v>28.31678231234336</v>
+      </c>
+      <c r="AL41">
+        <f>AH41+AK41</f>
+        <v>60.166782312343358</v>
+      </c>
     </row>
-    <row r="42" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>37</v>
       </c>
@@ -5706,8 +6564,28 @@
       <c r="AE42" t="s">
         <v>131</v>
       </c>
+      <c r="AH42">
+        <f>0.65*J42</f>
+        <v>37.700000000000003</v>
+      </c>
+      <c r="AI42" s="4">
+        <f>1-(AH42^2/2025)</f>
+        <v>0.29812839506172828</v>
+      </c>
+      <c r="AJ42">
+        <f>G42-(2/3*L42)</f>
+        <v>16.333333333333336</v>
+      </c>
+      <c r="AK42">
+        <f>2*((5*AJ42)/(SQRT(((H42+AH42)/2)+AJ42)))</f>
+        <v>22.942579243483667</v>
+      </c>
+      <c r="AL42">
+        <f>AH42+AK42</f>
+        <v>60.642579243483667</v>
+      </c>
     </row>
-    <row r="43" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>2</v>
       </c>
@@ -5805,8 +6683,28 @@
       <c r="AE43" t="s">
         <v>131</v>
       </c>
+      <c r="AH43">
+        <f>0.65*J43</f>
+        <v>26.650000000000002</v>
+      </c>
+      <c r="AI43" s="5">
+        <f>1-(AH43^2/2025)</f>
+        <v>0.64927283950617287</v>
+      </c>
+      <c r="AJ43">
+        <f>G43-(2/3*L43)</f>
+        <v>20</v>
+      </c>
+      <c r="AK43">
+        <f>2*((5*AJ43)/(SQRT(((H43+AH43)/2)+AJ43)))</f>
+        <v>26.767981889860298</v>
+      </c>
+      <c r="AL43">
+        <f>AH43+AK43</f>
+        <v>53.4179818898603</v>
+      </c>
     </row>
-    <row r="44" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>7</v>
       </c>
@@ -5904,8 +6802,28 @@
       <c r="AE44" t="s">
         <v>133</v>
       </c>
+      <c r="AH44">
+        <f>0.65*J44</f>
+        <v>27.95</v>
+      </c>
+      <c r="AI44" s="5">
+        <f>1-(AH44^2/2025)</f>
+        <v>0.61422098765432098</v>
+      </c>
+      <c r="AJ44">
+        <f>G44-(2/3*L44)</f>
+        <v>15</v>
+      </c>
+      <c r="AK44">
+        <f>2*((5*AJ44)/(SQRT(((H44+AH44)/2)+AJ44)))</f>
+        <v>20.806259464411976</v>
+      </c>
+      <c r="AL44">
+        <f>AH44+AK44</f>
+        <v>48.756259464411976</v>
+      </c>
     </row>
-    <row r="45" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>1</v>
       </c>
@@ -6003,8 +6921,28 @@
       <c r="AE45" t="s">
         <v>133</v>
       </c>
+      <c r="AH45">
+        <f>0.65*J45</f>
+        <v>31.200000000000003</v>
+      </c>
+      <c r="AI45" s="5">
+        <f>1-(AH45^2/2025)</f>
+        <v>0.5192888888888888</v>
+      </c>
+      <c r="AJ45">
+        <f>G45-(2/3*L45)</f>
+        <v>10.666666666666668</v>
+      </c>
+      <c r="AK45">
+        <f>2*((5*AJ45)/(SQRT(((H45+AH45)/2)+AJ45)))</f>
+        <v>16.604623344850086</v>
+      </c>
+      <c r="AL45">
+        <f>AH45+AK45</f>
+        <v>47.804623344850086</v>
+      </c>
     </row>
-    <row r="46" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>48</v>
       </c>
@@ -6102,8 +7040,28 @@
       <c r="AE46" t="s">
         <v>133</v>
       </c>
+      <c r="AH46">
+        <f>0.65*J46</f>
+        <v>31.200000000000003</v>
+      </c>
+      <c r="AI46" s="5">
+        <f>1-(AH46^2/2025)</f>
+        <v>0.5192888888888888</v>
+      </c>
+      <c r="AJ46">
+        <f>G46-(2/3*L46)</f>
+        <v>4</v>
+      </c>
+      <c r="AK46">
+        <f>2*((5*AJ46)/(SQRT(((H46+AH46)/2)+AJ46)))</f>
+        <v>6.7515957805577775</v>
+      </c>
+      <c r="AL46" s="3">
+        <f>AH46+AK46</f>
+        <v>37.951595780557781</v>
+      </c>
     </row>
-    <row r="47" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>35</v>
       </c>
@@ -6201,8 +7159,28 @@
       <c r="AE47" t="s">
         <v>133</v>
       </c>
+      <c r="AH47">
+        <f>0.65*J47</f>
+        <v>13</v>
+      </c>
+      <c r="AI47" s="5">
+        <f>1-(AH47^2/2025)</f>
+        <v>0.91654320987654325</v>
+      </c>
+      <c r="AJ47" s="3">
+        <f>G47-(2/3*L47)</f>
+        <v>-5.3333333333333321</v>
+      </c>
+      <c r="AK47">
+        <f>2*((5*AJ47)/(SQRT(((H47+AH47)/2)+AJ47)))</f>
+        <v>-14.169838168641521</v>
+      </c>
+      <c r="AL47" s="3">
+        <f>AH47+AK47</f>
+        <v>-1.1698381686415207</v>
+      </c>
     </row>
-    <row r="48" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>27</v>
       </c>
@@ -6303,8 +7281,28 @@
       <c r="AG48" t="s">
         <v>158</v>
       </c>
+      <c r="AH48">
+        <f>0.65*J48</f>
+        <v>29.900000000000002</v>
+      </c>
+      <c r="AI48" s="5">
+        <f>1-(AH48^2/2025)</f>
+        <v>0.55851358024691355</v>
+      </c>
+      <c r="AJ48">
+        <f>G48-(2/3*L48)</f>
+        <v>10</v>
+      </c>
+      <c r="AK48">
+        <f>2*((5*AJ48)/(SQRT(((H48+AH48)/2)+AJ48)))</f>
+        <v>16.795459121697256</v>
+      </c>
+      <c r="AL48">
+        <f>AH48+AK48</f>
+        <v>46.695459121697255</v>
+      </c>
     </row>
-    <row r="49" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>0</v>
       </c>
@@ -6402,8 +7400,28 @@
       <c r="AE49" t="s">
         <v>133</v>
       </c>
+      <c r="AH49">
+        <f>0.65*J49</f>
+        <v>44.85</v>
+      </c>
+      <c r="AI49" s="4">
+        <f>1-(AH49^2/2025)</f>
+        <v>6.6555555555555257E-3</v>
+      </c>
+      <c r="AJ49">
+        <f>G49-(2/3*L49)</f>
+        <v>17.666666666666668</v>
+      </c>
+      <c r="AK49">
+        <f>2*((5*AJ49)/(SQRT(((H49+AH49)/2)+AJ49)))</f>
+        <v>24.132703835081315</v>
+      </c>
+      <c r="AL49">
+        <f>AH49+AK49</f>
+        <v>68.98270383508131</v>
+      </c>
     </row>
-    <row r="50" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>11</v>
       </c>
@@ -6501,8 +7519,28 @@
       <c r="AE50" t="s">
         <v>133</v>
       </c>
+      <c r="AH50">
+        <f>0.65*J50</f>
+        <v>14.950000000000001</v>
+      </c>
+      <c r="AI50" s="5">
+        <f>1-(AH50^2/2025)</f>
+        <v>0.88962839506172842</v>
+      </c>
+      <c r="AJ50">
+        <f>G50-(2/3*L50)</f>
+        <v>8.3333333333333357</v>
+      </c>
+      <c r="AK50">
+        <f>2*((5*AJ50)/(SQRT(((H50+AH50)/2)+AJ50)))</f>
+        <v>15.526003767242434</v>
+      </c>
+      <c r="AL50" s="3">
+        <f>AH50+AK50</f>
+        <v>30.476003767242435</v>
+      </c>
     </row>
-    <row r="51" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>29</v>
       </c>
@@ -6600,10 +7638,30 @@
       <c r="AE51" t="s">
         <v>133</v>
       </c>
+      <c r="AH51">
+        <f>0.65*J51</f>
+        <v>17.55</v>
+      </c>
+      <c r="AI51" s="5">
+        <f>1-(AH51^2/2025)</f>
+        <v>0.84789999999999999</v>
+      </c>
+      <c r="AJ51">
+        <f>G51-(2/3*L51)</f>
+        <v>24.666666666666668</v>
+      </c>
+      <c r="AK51">
+        <f>2*((5*AJ51)/(SQRT(((H51+AH51)/2)+AJ51)))</f>
+        <v>34.904301323020519</v>
+      </c>
+      <c r="AL51">
+        <f>AH51+AK51</f>
+        <v>52.454301323020516</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AD51" xr:uid="{C0EA501B-F4E9-40F5-BCE6-EA7716C70CE7}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AD51">
+  <autoFilter ref="A1:AL51" xr:uid="{C0EA501B-F4E9-40F5-BCE6-EA7716C70CE7}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AL51">
       <sortCondition descending="1" ref="AD1:AD51"/>
     </sortState>
   </autoFilter>
